--- a/DOSSIES_MULTIFORMATO/POLÍCIA_CIVIL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/POLÍCIA_CIVIL/dossie.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,4634 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>Descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2017NE00652</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31/08/2017</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>170357.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERV.DE INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÉCN.EM TELECOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2014NE01164</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31/07/2014</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>212379.42</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Contrato No. 2/2011 - Process Sist CCCA - Cadastro Civil do Amazonas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014NE00432</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>31/03/2014</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>131953.68</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Contrato No. 2/2011 - Process Sist CCCA - Cadastro Civil do Amazonas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2019NE00911</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30/12/2019</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019NE00913</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30/12/2019</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019NE00910</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30/12/2019</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018NE01040</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30/07/2018</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>22294.66</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018NE01039</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8/2007</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30/07/2018</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2302.86</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025NE0000347</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30/04/2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>215739.02</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2015NE01163</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>29/09/2015</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>70793.42</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PROCESSAMENTO DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2015NE01154</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>29/09/2015</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3477.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>REF. PROCESSAMENTO DE DADOS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2015NE01159</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>29/09/2015</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7593.9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PROCESSAMENTOS DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2015NE01162</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>29/09/2015</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>18492.51</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PROCESSAMENTOS DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2018NE01586</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28/12/2018</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>22294.66</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2017NE00788</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>28/11/2017</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>85178.55</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERV.DE INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÉCN.EM TELECOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2017NE00968</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>27/12/2017</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>25558.81</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023NE0000787</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>27/07/2023</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>39783.95</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023NE0000789</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>27/07/2023</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2018NE01025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>27/07/2018</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2018NE01028</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>27/07/2018</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2368.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2018NE01027</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>27/07/2018</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>761.84</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2018NE01024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>27/07/2018</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2018NE01026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>27/07/2018</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024NE0000105</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>46130.51</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024NE0001320</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>27802.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 235/2024, REFERENTE AO 2º TERMO ADITIVO AO CONTRATO Nº 02/2022, EM ATENDIMENTO AO DECRETO Nº 50.522, DE 22 DE OUTUBRO DE 2024, POR NÃO UTILIZAÇÃO DE SALDO PARA AJUSTE DO ENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024NE0001321</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4699.65</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 995/2024, REFERENTE AO 2º TERMO ADITIVO AO CONTRATO Nº 02/2022, EM ATENDIMENTO AO DECRETO Nº 50.522, DE 22 DE OUTUBRO DE 2024, POR NÃO UTILIZAÇÃO DE SALDO PARA AJUSTE DO ENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2018NE01555</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>26/12/2018</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2019NE00781</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>26/11/2019</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>92623.16</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022NE0000886</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>26/08/2022</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>415175.73</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇOS A EXECUÇÃO DOS SISTEMAS AM-CCCA, DE PROTOCOLO-SPROWEB, DE PESSOAL DA PC-SPPC, TÉCNICOS EM TELECOMUNICAÇÕES E DE INFORMATICA. PARA ATENDER AOS MESES DE JUN/JUL/AGO, REF. AO CONTRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023NE0000786</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>26/07/2023</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>39783.95</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL POR NÃO UTILIZAÇÃO DO SALDO DEVIDO AO TERMINO DO CONTRATO PRIMITIVO N° 02/2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2018NE01014</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2018NE00998</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2557.25</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2018NE01018</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2018NE01016</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2018NE01002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18492.17</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2018NE01013</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2018NE01019</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2018NE01015</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2018NE01005</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5362.58</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2018NE01012</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13008.48</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2018NE01009</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12839.43</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2018NE01011</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13126.77</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2018NE01000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3477.7</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2018NE01017</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>66899.52</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2018NE01007</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>91734.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2018NE01008</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13091.17</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2018NE01010</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13547.01</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2018NE01004</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7593.9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2018NE01006</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5689.97</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2018NE01001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3130.14</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2018NE01003</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P.238/2015</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>26/07/2018</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18492.17</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2018NE00990</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7313.51</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2018NE00982</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7/2007</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>63581.96</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados nos exercícios de 2010,2013,2014,2015 e 2016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2018NE00991</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14750.04</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2018NE00992</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19/2014</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>460.55</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2018NE00984</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>18492.17</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2018NE00994</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>63687.03</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2018NE00986</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1346.9</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2018NE00993</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>25/07/2018</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>169392.65</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Exercícios anteriores em favor da PRODAM referente a serviços contratuais de processamento de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025NE0000514</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>25/06/2025</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>215739.02</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024NE0000758</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>25/06/2024</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>269053.08</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2023NE0000384</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>25/04/2023</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>276783.82</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA, PARA ATENDER A PC/AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024NE0000374</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>25/03/2024</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024NE0000424</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>24/04/2024</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>269053.08</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL PARA AJUSTE NA DESCRIÇÃO DOS ITENS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024NE0000433</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>24/04/2024</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>269053.08</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025NE0000074</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>44842.18</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2015NE00416</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>23/03/2015</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CADASTRO CIVIL E CRIMINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2015NE00414</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>23/03/2015</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CADASTRO CIVIL E CRIMINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2015NE00413</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>23/03/2015</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SISTEMAS DE CADASTRO CIVIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2015NE00415</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>23/03/2015</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CADASTRO CIVIL E CRIMINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2022NE0001435</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>22/12/2022</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>27762.29</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL REFERENTE AO 5º TERMO ADITIVO AO CONTRATO Nº 004/2017 POR NÃO UTILIZAÇÃO DO SALDO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2015NE01331</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>18492.51</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2015NE01328</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>7593.9</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2015NE01302</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>18491.83</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2015NE01289</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2015NE01292</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>286.05</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2015NE01326</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3477.7</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2015NE01290</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2100.49</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2015NE01291</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>22/12/2015</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>830.71</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025NE0000806</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>106307.77</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2019NE00631</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>22/10/2019</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>92623.16</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2023NE0000919</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>276783.82</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2018NE01134</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>22/08/2018</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>713198.33</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CONTRATAÃ‡ÃƒO DE PRESTAÃ‡ÃƒO DE SERV.DE INFORM., COMPREENDENDO A EXECUÃ‡ÃƒO DOS SIST.DE CONTROLE DE CADSTRO CIVIL DO AM-CCCA,SIDT.DE PROTOCOLO-SPROWEB,SIST.DE PESSOAL DA PC-SPPC,PREST.DE SERV.TÃ‰CN.EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2018NE01133</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>22/08/2018</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>195909.59</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PRESTAÃ‡ÃƒO DE SERV.DE INFORMÃTICA, COMPREENDENDO A EXECUÃ‡ÃƒO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÃ‰CN.EM T</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024NE0000417</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>22/04/2024</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>269053.08</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2021NE0000504</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>21/10/2021</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>29541.28</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL REFERENTE AO TÉRMINO DE VIGÊNCIA DO 3º TERMO ADITIVO AO CONTRATO Nº 005/2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2022NE0000731</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>21/06/2022</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AM-CCCA, SISTEMA DE PROTOCOLO-SPROWEB, SISTEMA DE PESSOAL DA PC-SPPC, PRESTAÇ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2021NE0000577</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>19/11/2021</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO PARCIAL EM ATENDIMENTO AO 5º TERMO ADITIVO AO CONTRATO Nº 004/2017, QUE TRATA DO REALINHAMENTO E SUPRESÃO DO MESMO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2014NE00685</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>19/05/2014</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>35116.14</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Contrato No. 16/2013 - Acesso Comp Central/Internet em 5 Mbps e Firewall AKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2014NE00686</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>19/05/2014</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6750.24</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Contrato No. 7/2011 - Processamento Sistema Controle de Pessoal - CPPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2014NE00659</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>19/05/2014</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6263.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Contrato No. 6/2011 - Cessão de uso do Sistema de Protocolo-SPROWEB (06/11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2014NE00666</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>19/05/2014</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>65976.84</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Contrato No. 2/2011 - Process Sist CCCA - Cadastro Civil do Amazonas</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2018NE01095</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>17/08/2018</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2302.86</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024NE0000510</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>17/05/2024</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS -CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E PRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2015NE00539</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>17/04/2015</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>36984</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>PROCESSAMENTO DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2015NE00537</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>17/04/2015</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>141586</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>processamento de dados</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025NE0000234</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>129826.89</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2014NE01139</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>19/2014</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>15/07/2014</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15657.26</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Contrato No. 19/2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2019NE00737</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>14/11/2019</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>92623.16</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2018NE01079</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>14/08/2018</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>195909.59</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>anulação total do saldo da NE 00078/2018 de 02/01/2018, para - Regularização contábil para correção da natureza de despesa empenhada. (Orientação Técnica GINS n° 12/2018 e Portaria Conjunta n°2 STN qu</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2018NE01094</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>14/08/2018</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>713198.33</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Anulação Total da NE 306/18 de 10/03/2018 para Regularização contábil para correção da natureza de despesa empenhada. (Orientação Técnica GINS n° 12/2018 e Portaria Conjunta n°2 STN que altera da Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2017NE00873</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>13/12/2017</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>85178.55</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERV.DE INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÉCN.EM TELECOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2016NE00563</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>12/12/2016</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>334497.6</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>REFERENTE PROCESSAMENTO DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2021NE0000543</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>11/11/2021</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>92623.16</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2021NE0000409</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10/09/2021</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>185246.32</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2016NE00283</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10/06/2016</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>334497.6</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ANALAÇÃO TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025NE0000118</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>179782.52</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2023NE0000103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10/03/2023</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>230653.31</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>PARA ATENDER AO 1º TA AO CT 02/2022, VIGÊNCIA 10/03/2023 A 10/03/2024, REF. CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA, PARA ATENDER A PC/AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2018NE00306</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10/03/2018</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>713198.33</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERV.DE INFORM., COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADSTRO CIVIL DO AM-CCCA,SIDT.DE PROTOCOLO-SPROWEB,SIST.DE PESSOAL DA PC-SPPC,PREST.DE SERV.TÉCN.EM TELECO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2017NE00173</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10/03/2017</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>170357.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERV.DE INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÉCN.EM TELECOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025NE0000758</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>107869.51</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2022NE0000150</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>09/03/2022</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>92261.39999999999</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2021NE0000081</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>09/03/2021</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>157459.37</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2020NE00100</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>09/03/2020</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>898444.65</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025NE0000755</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>108178.94</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N°005/2025, REFERENTE AO TÉRMINO DE VIGÊNCIA DO 2° TERMO ADITIVO AO CONTRATO 002/2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2019NE00447</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>08/08/2019</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>277869.48</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO TOTAL DA NE 445/19 - ERRO NA REFERÊNCIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2019NE00448</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>08/08/2019</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>277869.48</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2014NE01183</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>08/08/2014</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>51348.42</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Contrato No. 16/2013 - Acesso Comp Central/Internet em 5 Mbps e Firewall AKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2019NE00445</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>07/08/2019</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>277869.48</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2016NE00282</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>07/06/2016</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>334497.6</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS EM SISTEMA DE CONTROLE DE CADASTRO CIVIL E CRIMINAL, 5º TERMO ADITIVO AO CONTRATO Nº 02/11, MESES DE JANEIRO A MAIO/2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2024NE0000235</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>07/03/2024</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>224210.9</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2021NE0000459</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>06/10/2021</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>92623.16</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2018NE01045</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>06/08/2018</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2021NE0000292</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>06/07/2021</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>185246.32</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2024NE0000478</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>06/05/2024</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2021NE0000195</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>05/05/2021</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>185246.32</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - EPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2022NE0000481</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>05/04/2022</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>138391.91</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AM-CCCA, SISTEMA DE PROTOCOLO-SPROWEB, SISTEMA DE PESSOAL DA PC-SPPC, PRESTAÇ</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2015NE00020</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>18492.17</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2015NE00013</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>19/2014</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ref. a serviços de processamentos de dados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2015NE00012</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>19/2014</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ref. a serviços de processamento de dados</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2015NE00023</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3539.82</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2015NE00014</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>70793.14</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PROCESSAMENTO DE DADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2015NE00017</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>05/01/2015</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>3284.53</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2022NE0001059</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>04/10/2022</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>276783.82</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇOS A EXECUÇÃO DOS SISTEMAS AM-CCCA, DE PROTOCOLO-SPROWEB, DE PESSOAL DA PC-SPPC, TÉCNICOS EM TELECOMUNICAÇÕES E DE INFORMATICA. PARA ATENDER AOS MESES DE SET E OUT/2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2024NE0000995</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>04/09/2024</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>134526.54</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2021NE0000001</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>04/01/2021</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>213033.27</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWEB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO </t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026NE0000084</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>179782.52</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2022NE0000042</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>212835.79</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVIÇO DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E </t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025NE0000669</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>107869.51</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E </t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2022NE0000621</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>02/06/2022</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>4612.86</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AM-CCCA, SISTEMA DE PROTOCOLO-SPROWEB, SISTEMA DE PESSOAL DA PC-SPPC, PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES </t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2017NE00271</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>02/05/2017</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>340714.2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>REFERENTE SERVIÇOS DE INFORMÁTICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025NE0000005</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>269053.08</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2024NE0000049</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>02/01/2024</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>276783.82</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2024NE0000048</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>02/01/2024</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>207588.88</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO TOTAL DA NE Nº 004/2024, EM ATENDIMENTO AO PARECER Nº 97/2024 ? PJ/PC/AM, ÀS FLS. 177 A 180 DO PROCESSO SIGED Nº 016449/2023-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2024NE0000004</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>02/01/2024</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>207588.88</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA, EXEC. DOS SIST. DE CONTROLE DE CADASTRO CIVIL DO AM; SIST. DE PROT SPROWEB, SIST. DE PESSOAL DA PC SPPC, PREST. DE SERV. TÉC. EM TELEC. E SERV. EVENTUAIS DE INFORMÁTICA, PARA ATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2023NE0000014</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>02/01/2023</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>322914.33</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SERV. DE INFORMÁTICA COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO ESTADO DO AMAZONAS - CCCA, SISTEMAS DE PROTOCOLO - SPROWEB, SISTEMAS DE PESSOAL DA POLICIA CIVIL - SPPC E PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2020NE00001</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>02/01/2020</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>213033.27</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO D</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2019NE00001</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>02/01/2019</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>213033.27</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERV.DE INFORM., COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADSTRO CIVIL DO AM-CCCA,SIDT.DE PROTOCOLO-SPROWEB,SIST.DE PESSOAL DA PC-SPPC,PREST.DE SERV.TÉCN.EM TELECO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2018NE00078</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>02/01/2018</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>195910.69</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERV.DE INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DOS SIST.DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS CCCA, SIST.DE PROTOCOLO SPROWEB, SIST.DE PESSOAL DA PC SPPC, PREST.DE SERV.TÉCN.EM TELECOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2014NE00065</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>02/01/2014</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>131953.68</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Contrato No. 2/2011 - Process Sist CCCA - Cadastro Civil do Amazonas</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2014NE00035</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>02/01/2014</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>6263.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Contrato No. 6/2011 - Cessão de uso do Sistema de Protocolo-SPROWEB (06/11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2014NE00034</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7/2011</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>02/01/2014</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>6750.24</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Contrato No. 7/2011 - Processamento Sistema Controle de Pessoal - CPPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2014NE00036</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>16/2013</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>02/01/2014</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>35116.14</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Contrato No. 16/2013 - Acesso Comp Central/Internet em 5 Mbps e Firewall AKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2015NE01259</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>01/12/2015</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>70792.86</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2015NE01264</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>01/12/2015</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>70793.42</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2014NE01205</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>23/2014</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>01/08/2014</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>6169.59</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Contrato No. 23/2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2019NE00163</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>01/04/2019</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>277869.48</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO D</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2019NE00123</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>01/03/2019</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>64836.21</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DE INFORMÁTICAS COMPREENDENDO A EXECUÇÃO DOS SISTEMAS DE CONTROLE DE CADASTRO CIVIL DO AMAZONAS - CCCA, SISTEMA DE PROTOCOLO - SPROWB, SISTEMA DE PESSOAL DA POLÍCIA CIVIL - SPPC E PRESTAÇÃO D</t>
         </is>
       </c>
     </row>
@@ -644,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +5315,690 @@
         <is>
           <t>EmpenhosVinc</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>137923</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>34482</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12/2022</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>115821.4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>137170</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>33692</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11/2022</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>115703.2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>155102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>50245</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>83477.38</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>107937</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5881</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12/2018</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>71298.16</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>107292</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4/2017</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11/2018</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>71190.44</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>156047</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>51233</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>70129.59</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>167388</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>52391.54</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>154904</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50244</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10136.76</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>155437</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10136.76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>154905</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50248</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6360.23</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>155438</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>51236</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6360.23</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>167390</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4641</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>155987</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>51234</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1653.5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>154805</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50246</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1634.04</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>167387</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1425.39</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>154906</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>50247</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1167.84</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>155439</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51235</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1167.84</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLETA</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>167389</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2/2022</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>872.67</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -700,9 +6012,790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Atraso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Corrigido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>004/2017</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>107292</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11/2018</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>71.190,44</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2661 dias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>004/2017</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>107937</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12/2018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>71.298,16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2632 dias</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>137170</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>11/2022</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>115.703,20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1203 dias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>137923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12/2022</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>115.821,40</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1172 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Acesso Gerenciado à Rede Mundial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>154904</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.136,76</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>472 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>155102</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>83.477,38</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>472 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>154805</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.634,04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>472 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gestão de Segurança e Ativos de Rede</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>154905</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6.360,23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>472 dias</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>154906</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.167,84</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>472 dias</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>155987</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.653,50</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>441 dias</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>155439</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.167,84</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>441 dias</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gestão de Segurança e Ativos de Rede</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>155438</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6.360,23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>441 dias</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>156047</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.129,59</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>441 dias</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Acesso Gerenciado à Rede Mundial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>002/2022</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>155437</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10.136,76</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>441 dias</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DOSSIES_MULTIFORMATO/POLÍCIA_CIVIL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/POLÍCIA_CIVIL/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2027-12-31</t>
         </is>
       </c>
     </row>
